--- a/repair/back/doc/estimate/periodic1.xlsx
+++ b/repair/back/doc/estimate/periodic1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild=""/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="731" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="21" r:id="rId1"/>
@@ -373,7 +373,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t>식</t>
   </si>
@@ -1831,6 +1831,12 @@
   <si>
     <t xml:space="preserve">다. 점 검 범 위  : </t>
   </si>
+  <si>
+    <t>「시설물의 안전 및 유지관리에 관한 특별법」(이하 “시설물안전법”이라 한다) 제11조, 제12조 및</t>
+  </si>
+  <si>
+    <t>동법 시행령 제8조에 따라</t>
+  </si>
 </sst>
 </file>
 
@@ -1908,7 +1914,7 @@
     <numFmt numFmtId="243" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="244" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="146">
+  <fonts count="147">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -2578,12 +2584,6 @@
       <color rgb="FFFA7D00"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color theme="1"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="돋움"/>
       <color rgb="FF006100"/>
@@ -2642,16 +2642,6 @@
       <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <color theme="1"/>
@@ -2696,6 +2686,27 @@
       <sz val="12.0"/>
       <name val="맑은 고딕"/>
       <color theme="1"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24.0"/>
+      <name val="바탕"/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="42">
@@ -4071,7 +4082,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4080,7 +4090,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4089,7 +4098,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4098,7 +4106,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4113,7 +4120,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4128,7 +4134,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -4143,7 +4148,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4152,7 +4156,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -4163,7 +4166,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3161">
@@ -13605,19 +13607,19 @@
     <xf numFmtId="0" fontId="123" fillId="0" borderId="105" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="106" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="106" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13626,10 +13628,10 @@
     <xf numFmtId="0" fontId="110" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13638,10 +13640,10 @@
     <xf numFmtId="0" fontId="110" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13650,10 +13652,10 @@
     <xf numFmtId="0" fontId="110" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13662,10 +13664,10 @@
     <xf numFmtId="0" fontId="110" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="35" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13674,10 +13676,10 @@
     <xf numFmtId="0" fontId="110" fillId="36" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="37" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="38" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="39" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
@@ -13686,14 +13688,14 @@
     <xf numFmtId="0" fontId="110" fillId="40" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="127" fillId="41" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="371">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -14777,6 +14779,27 @@
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3162">
@@ -18949,7 +18972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="D1:AH1591"/>
+  <dimension ref="D1:AF1591"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.500000"/>
   <cols>
     <col min="1" max="3" style="90" width="8.78277800" customWidth="1" outlineLevel="0"/>
@@ -18958,11 +18981,10 @@
     <col min="13" max="31" style="90" width="3.33833334" customWidth="1" outlineLevel="0"/>
     <col min="32" max="32" style="90" width="2.33833334" customWidth="1" outlineLevel="0"/>
     <col min="33" max="259" style="90" width="6.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="260" max="260" style="90" width="8.78277800" customWidth="1" outlineLevel="0"/>
-    <col min="261" max="16384" style="90" width="8.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="260" max="16384" style="90" width="8.78277800" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:34" s="96" customFormat="1" ht="42.000000" customHeight="1">
+    <row r="1" spans="4:31" s="96" customFormat="1" ht="42.000000" customHeight="1">
       <c r="D1" s="306" t="s">
         <v>84</v>
       </c>
@@ -18994,7 +19016,7 @@
       <c r="AD1" s="306"/>
       <c r="AE1" s="306"/>
     </row>
-    <row r="2" spans="4:34" s="96" customFormat="1" ht="12.000000" customHeight="1">
+    <row r="2" spans="4:31" s="96" customFormat="1" ht="12.000000" customHeight="1">
       <c r="D2" s="132"/>
       <c r="E2" s="132"/>
       <c r="F2" s="132"/>
@@ -19024,7 +19046,7 @@
       <c r="AD2" s="133"/>
       <c r="AE2" s="133"/>
     </row>
-    <row r="3" spans="4:34" s="96" customFormat="1" ht="18.000000" customHeight="1">
+    <row r="3" spans="4:31" s="96" customFormat="1" ht="18.000000" customHeight="1">
       <c r="D3" s="307" t="s">
         <v>175</v>
       </c>
@@ -19056,7 +19078,7 @@
       <c r="AD3" s="307"/>
       <c r="AE3" s="307"/>
     </row>
-    <row r="4" spans="4:34" s="96" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="4" spans="4:31" s="96" customFormat="1" ht="7.500000" customHeight="1">
       <c r="D4" s="134"/>
       <c r="E4" s="134"/>
       <c r="F4" s="134"/>
@@ -19086,7 +19108,7 @@
       <c r="AD4" s="135"/>
       <c r="AE4" s="135"/>
     </row>
-    <row r="5" spans="4:34" s="96" customFormat="1" ht="5.000000" customHeight="1">
+    <row r="5" spans="4:31" s="96" customFormat="1" ht="5.000000" customHeight="1">
       <c r="D5" s="132"/>
       <c r="E5" s="132"/>
       <c r="F5" s="132"/>
@@ -19116,7 +19138,7 @@
       <c r="AD5" s="133"/>
       <c r="AE5" s="133"/>
     </row>
-    <row r="6" spans="4:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="6" spans="4:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D6" s="308" t="s">
         <v>83</v>
       </c>
@@ -19150,7 +19172,7 @@
       <c r="AD6" s="132"/>
       <c r="AE6" s="132"/>
     </row>
-    <row r="7" spans="4:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="7" spans="4:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D7" s="308" t="s">
         <v>81</v>
       </c>
@@ -19184,7 +19206,7 @@
       <c r="AD7" s="132"/>
       <c r="AE7" s="132"/>
     </row>
-    <row r="8" spans="4:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="8" spans="4:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D8" s="308" t="s">
         <v>80</v>
       </c>
@@ -19218,7 +19240,7 @@
       <c r="AD8" s="309"/>
       <c r="AE8" s="309"/>
     </row>
-    <row r="9" spans="4:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="9" spans="4:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D9" s="308" t="s">
         <v>79</v>
       </c>
@@ -19230,32 +19252,8 @@
       </c>
       <c r="I9" s="138"/>
       <c r="J9" s="138"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="96"/>
-      <c r="R9" s="96"/>
-      <c r="S9" s="96"/>
-      <c r="T9" s="96"/>
-      <c r="U9" s="96"/>
-      <c r="V9" s="96"/>
-      <c r="W9" s="96"/>
-      <c r="X9" s="96"/>
-      <c r="Y9" s="96"/>
-      <c r="Z9" s="96"/>
-      <c r="AA9" s="96"/>
-      <c r="AB9" s="96"/>
-      <c r="AC9" s="96"/>
-      <c r="AD9" s="96"/>
-      <c r="AE9" s="96"/>
-      <c r="AF9" s="96"/>
-      <c r="AG9" s="96"/>
-      <c r="AH9" s="96"/>
-    </row>
-    <row r="10" spans="4:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    </row>
+    <row r="10" spans="4:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D10" s="308" t="s">
         <v>77</v>
       </c>
@@ -19289,7 +19287,7 @@
       <c r="AD10" s="309"/>
       <c r="AE10" s="309"/>
     </row>
-    <row r="11" spans="4:34" s="96" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
+    <row r="11" spans="4:31" s="96" customFormat="1" ht="13.500000" hidden="1" customHeight="1">
       <c r="D11" s="139"/>
       <c r="E11" s="139"/>
       <c r="F11" s="139"/>
@@ -19319,7 +19317,7 @@
       <c r="AD11" s="139"/>
       <c r="AE11" s="139"/>
     </row>
-    <row r="12" spans="4:34" s="96" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="12" spans="4:31" s="96" customFormat="1" ht="7.500000" customHeight="1">
       <c r="D12" s="134"/>
       <c r="E12" s="134"/>
       <c r="F12" s="134"/>
@@ -19349,7 +19347,7 @@
       <c r="AD12" s="134"/>
       <c r="AE12" s="134"/>
     </row>
-    <row r="13" spans="4:34" s="96" customFormat="1" ht="11.250000" customHeight="1">
+    <row r="13" spans="4:31" s="96" customFormat="1" ht="11.250000" customHeight="1">
       <c r="D13" s="132"/>
       <c r="E13" s="132"/>
       <c r="F13" s="132"/>
@@ -19379,7 +19377,7 @@
       <c r="AD13" s="132"/>
       <c r="AE13" s="132"/>
     </row>
-    <row r="14" spans="4:34" s="96" customFormat="1" ht="20.000000" customHeight="1">
+    <row r="14" spans="4:31" s="96" customFormat="1" ht="20.000000" customHeight="1">
       <c r="D14" s="311" t="s">
         <v>237</v>
       </c>
@@ -19411,7 +19409,7 @@
       <c r="AD14" s="311"/>
       <c r="AE14" s="311"/>
     </row>
-    <row r="15" spans="4:34" s="96" customFormat="1" ht="10.000000" customHeight="1">
+    <row r="15" spans="4:31" s="96" customFormat="1" ht="10.000000" customHeight="1">
       <c r="D15" s="132"/>
       <c r="E15" s="132"/>
       <c r="F15" s="132"/>
@@ -19441,7 +19439,7 @@
       <c r="AD15" s="132"/>
       <c r="AE15" s="132"/>
     </row>
-    <row r="16" spans="4:34" s="96" customFormat="1" ht="63.750000" customHeight="1">
+    <row r="16" spans="4:31" s="96" customFormat="1" ht="63.750000" customHeight="1">
       <c r="D16" s="136" t="s">
         <v>238</v>
       </c>
@@ -34209,10 +34207,10 @@
     <mergeCell ref="D20:AE20"/>
     <mergeCell ref="H21:M21"/>
     <mergeCell ref="N21:AE21"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:AE22"/>
     <mergeCell ref="H23:M23"/>
     <mergeCell ref="N23:AE23"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:AE22"/>
     <mergeCell ref="H24:M24"/>
     <mergeCell ref="N24:AE24"/>
     <mergeCell ref="H25:M25"/>
@@ -34311,9 +34309,9 @@
         <v>30</v>
       </c>
       <c r="C5" s="329"/>
-      <c r="D5" s="330" t="e">
+      <c r="D5" s="330">
         <f>"일금 "&amp;NUMBERSTRING(H30,1)&amp;"원정"&amp;TEXT(H30,"(￦ #,##0)")&amp;" "</f>
-        <v>일금 #VALUE!원정</v>
+        <v/>
       </c>
       <c r="E5" s="330"/>
       <c r="F5" s="330"/>
@@ -36173,7 +36171,7 @@
     </row>
     <row r="59" spans="2:21" ht="24.950000" customHeight="1">
       <c r="B59" s="224" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="C59" s="224"/>
       <c r="D59" s="224"/>
@@ -36196,25 +36194,25 @@
       <c r="U59" s="224"/>
     </row>
     <row r="60" spans="2:21" ht="24.950000" customHeight="1">
-      <c r="B60" s="223" t="s">
-        <v>231</v>
-      </c>
-      <c r="C60" s="223"/>
-      <c r="D60" s="223"/>
-      <c r="E60" s="223"/>
-      <c r="F60" s="223"/>
-      <c r="G60" s="223"/>
-      <c r="H60" s="223"/>
-      <c r="I60" s="223"/>
-      <c r="J60" s="225" t="str">
+      <c r="B60" s="370" t="s">
+        <v>257</v>
+      </c>
+      <c r="C60" s="370"/>
+      <c r="D60" s="370"/>
+      <c r="E60" s="370"/>
+      <c r="F60" s="370"/>
+      <c r="G60" s="370"/>
+      <c r="H60" s="370"/>
+      <c r="I60" s="369" t="str">
         <f>B9</f>
         <v>효성뉴서울5차아파트</v>
       </c>
-      <c r="K60" s="225"/>
-      <c r="L60" s="225"/>
-      <c r="M60" s="225"/>
-      <c r="N60" s="225"/>
-      <c r="O60" s="225"/>
+      <c r="J60" s="369"/>
+      <c r="K60" s="369"/>
+      <c r="L60" s="369"/>
+      <c r="M60" s="369"/>
+      <c r="N60" s="369"/>
+      <c r="O60" s="369"/>
       <c r="P60" s="223" t="s">
         <v>234</v>
       </c>
@@ -36351,7 +36349,7 @@
     </row>
     <row r="68" spans="2:21" ht="20.000000" customHeight="1">
       <c r="C68" s="115" t="str">
-        <f>"② 위      치 : "&amp;E54</f>
+        <f>"② 위      치 : "&amp;갑지!N22</f>
         <v>② 위      치 : 인천 계양구 아나지로 199 (효성동)</v>
       </c>
       <c r="D68" s="115"/>
@@ -38471,8 +38469,8 @@
     <mergeCell ref="B56:U56"/>
     <mergeCell ref="B57:U57"/>
     <mergeCell ref="B59:U59"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="J60:O60"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="I60:O60"/>
     <mergeCell ref="P60:U60"/>
     <mergeCell ref="B61:U61"/>
     <mergeCell ref="B63:J63"/>

--- a/repair/back/doc/estimate/periodic1.xlsx
+++ b/repair/back/doc/estimate/periodic1.xlsx
@@ -1914,7 +1914,7 @@
     <numFmt numFmtId="243" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="244" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </numFmts>
-  <fonts count="147">
+  <fonts count="152">
     <font>
       <sz val="11.0"/>
       <name val="돋움"/>
@@ -2706,6 +2706,32 @@
       <b/>
       <sz val="24.0"/>
       <name val="바탕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
     </font>
   </fonts>
@@ -34920,8 +34946,8 @@
   <pageMargins left="0.79" right="0.79" top="0.59" bottom="0.39" header="0.31" footer="0.31"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait"/>
   <colBreaks count="2" manualBreakCount="2">
+    <brk id="9" max="35" man="1"/>
     <brk id="9" max="1048575" man="1"/>
-    <brk id="9" max="35" man="1"/>
   </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -38007,8 +38033,8 @@
       </c>
       <c r="Q146" s="88"/>
       <c r="R146" s="285">
-        <f>R137*P146%</f>
-        <v>109268.6</v>
+        <f>ROUND(R137*P146%,0)</f>
+        <v>109269</v>
       </c>
       <c r="S146" s="285"/>
       <c r="T146" s="285"/>
@@ -38041,8 +38067,8 @@
       </c>
       <c r="Q147" s="88"/>
       <c r="R147" s="288">
-        <f>(R137+R146)*P147%</f>
-        <v>120195.46</v>
+        <f>ROUND((R137+R146)*P147%,0)</f>
+        <v>120196</v>
       </c>
       <c r="S147" s="288"/>
       <c r="T147" s="288"/>
@@ -38068,7 +38094,7 @@
       <c r="P148" s="80"/>
       <c r="Q148" s="80"/>
       <c r="R148" s="292">
-        <f>SUM(R150:R154)</f>
+        <f>INT(SUM(R150:R154))</f>
         <v>219268</v>
       </c>
       <c r="S148" s="292"/>
@@ -38279,7 +38305,7 @@
       <c r="Q156" s="88"/>
       <c r="R156" s="303">
         <f>R137+R146+R147+R148</f>
-        <v>1541418.06</v>
+        <v>1541419</v>
       </c>
       <c r="S156" s="303"/>
       <c r="T156" s="303"/>
